--- a/divya-mam-excel.xlsx
+++ b/divya-mam-excel.xlsx
@@ -9,15 +9,26 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18975" windowHeight="7800" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18975" windowHeight="7800" firstSheet="2" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet5" sheetId="5" r:id="rId3"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId4"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId5"/>
+    <sheet name="Sheet6" sheetId="7" r:id="rId3"/>
+    <sheet name="vlookup" sheetId="6" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId6"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId7"/>
+    <sheet name="HLOOKUP" sheetId="8" r:id="rId8"/>
   </sheets>
+  <definedNames>
+    <definedName name="BillNo1">Sheet4!$A$151:$C$155</definedName>
+    <definedName name="BillNo2">Sheet4!$E$151:$G$155</definedName>
+    <definedName name="BillNo3">Sheet4!$J$151:$L$155</definedName>
+    <definedName name="res">HLOOKUP!$A$13:$F$18</definedName>
+    <definedName name="resu">HLOOKUP!$A$13:$F$18</definedName>
+    <definedName name="result">Sheet4!$A$80:$F$84</definedName>
+  </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -28,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="259">
   <si>
     <t>July 1, 2023</t>
   </si>
@@ -625,13 +636,193 @@
   </si>
   <si>
     <t>1.Vlookup in the same sheet.</t>
+  </si>
+  <si>
+    <t>vlookup with trim function</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        Anu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jatin     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">       Deepak     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Sam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       Seema </t>
+  </si>
+  <si>
+    <t>vlookup with Define Name</t>
+  </si>
+  <si>
+    <t>vllokup with column function</t>
+  </si>
+  <si>
+    <t>Range Vlookup</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Performance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target </t>
+  </si>
+  <si>
+    <t>Poor</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Avg</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Best</t>
+  </si>
+  <si>
+    <t>Sup</t>
+  </si>
+  <si>
+    <t>performance</t>
+  </si>
+  <si>
+    <t>0-34</t>
+  </si>
+  <si>
+    <t>35-59</t>
+  </si>
+  <si>
+    <t>60-79</t>
+  </si>
+  <si>
+    <t>80-89</t>
+  </si>
+  <si>
+    <t>90+</t>
+  </si>
+  <si>
+    <t>Co' Name</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Company ID contains</t>
+  </si>
+  <si>
+    <t>NMDC</t>
+  </si>
+  <si>
+    <t>NTPC</t>
+  </si>
+  <si>
+    <t>CC</t>
+  </si>
+  <si>
+    <t>NMDC Pvt. LTd</t>
+  </si>
+  <si>
+    <t>NTPC Ltd.</t>
+  </si>
+  <si>
+    <t>Vlookup with …………</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Neha</t>
+  </si>
+  <si>
+    <t>Mona</t>
+  </si>
+  <si>
+    <t>Ketan</t>
+  </si>
+  <si>
+    <t>Mumbai</t>
+  </si>
+  <si>
+    <t>Rollno.</t>
+  </si>
+  <si>
+    <t>Kolkata</t>
+  </si>
+  <si>
+    <t>Double Vlookup/Nested Vlookup</t>
+  </si>
+  <si>
+    <t>Vlookup from 2 tables</t>
+  </si>
+  <si>
+    <t>BillNo</t>
+  </si>
+  <si>
+    <t>Pencil</t>
+  </si>
+  <si>
+    <t>Keyboard</t>
+  </si>
+  <si>
+    <t>Mouse</t>
+  </si>
+  <si>
+    <t>CPU</t>
+  </si>
+  <si>
+    <t>Products</t>
+  </si>
+  <si>
+    <t>Chair</t>
+  </si>
+  <si>
+    <t>Table</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Steper</t>
+  </si>
+  <si>
+    <t>Penset</t>
+  </si>
+  <si>
+    <t>Vlookup from 2 tbale</t>
+  </si>
+  <si>
+    <t>vlookup from 3 tables</t>
+  </si>
+  <si>
+    <t>(dropdown)</t>
+  </si>
+  <si>
+    <t>Screen</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>Ac</t>
+  </si>
+  <si>
+    <t>LED</t>
+  </si>
+  <si>
+    <t>LCD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -671,6 +862,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="13">
@@ -747,7 +951,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -1122,11 +1326,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1202,6 +1434,27 @@
     <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1292,10 +1545,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1303,21 +1552,21 @@
   <dxfs count="2">
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1607,99 +1856,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="58" t="s">
+      <c r="B1" s="71"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="59"/>
-      <c r="I1" s="59"/>
-      <c r="J1" s="59"/>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="M1" s="59"/>
-      <c r="N1" s="59"/>
-      <c r="O1" s="59"/>
-      <c r="P1" s="59"/>
-      <c r="Q1" s="59"/>
-      <c r="R1" s="59"/>
-      <c r="S1" s="59"/>
-      <c r="T1" s="59"/>
-      <c r="U1" s="59"/>
-      <c r="V1" s="59"/>
-      <c r="W1" s="59"/>
-      <c r="X1" s="59"/>
-      <c r="Y1" s="59"/>
-      <c r="Z1" s="59"/>
-      <c r="AA1" s="59"/>
-      <c r="AB1" s="59"/>
-      <c r="AC1" s="59"/>
-      <c r="AD1" s="59"/>
-      <c r="AE1" s="59"/>
-      <c r="AF1" s="59"/>
-      <c r="AG1" s="59"/>
-      <c r="AH1" s="59"/>
-      <c r="AI1" s="60"/>
-      <c r="AJ1" s="64" t="s">
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
+      <c r="L1" s="80"/>
+      <c r="M1" s="80"/>
+      <c r="N1" s="80"/>
+      <c r="O1" s="80"/>
+      <c r="P1" s="80"/>
+      <c r="Q1" s="80"/>
+      <c r="R1" s="80"/>
+      <c r="S1" s="80"/>
+      <c r="T1" s="80"/>
+      <c r="U1" s="80"/>
+      <c r="V1" s="80"/>
+      <c r="W1" s="80"/>
+      <c r="X1" s="80"/>
+      <c r="Y1" s="80"/>
+      <c r="Z1" s="80"/>
+      <c r="AA1" s="80"/>
+      <c r="AB1" s="80"/>
+      <c r="AC1" s="80"/>
+      <c r="AD1" s="80"/>
+      <c r="AE1" s="80"/>
+      <c r="AF1" s="80"/>
+      <c r="AG1" s="80"/>
+      <c r="AH1" s="80"/>
+      <c r="AI1" s="81"/>
+      <c r="AJ1" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="AK1" s="67" t="s">
+      <c r="AK1" s="88" t="s">
         <v>14</v>
       </c>
-      <c r="AL1" s="70" t="s">
+      <c r="AL1" s="91" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="52"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="62"/>
-      <c r="K2" s="62"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="62"/>
-      <c r="N2" s="62"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="62"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="62"/>
-      <c r="W2" s="62"/>
-      <c r="X2" s="62"/>
-      <c r="Y2" s="62"/>
-      <c r="Z2" s="62"/>
-      <c r="AA2" s="62"/>
-      <c r="AB2" s="62"/>
-      <c r="AC2" s="62"/>
-      <c r="AD2" s="62"/>
-      <c r="AE2" s="62"/>
-      <c r="AF2" s="62"/>
-      <c r="AG2" s="62"/>
-      <c r="AH2" s="62"/>
-      <c r="AI2" s="63"/>
-      <c r="AJ2" s="65"/>
-      <c r="AK2" s="68"/>
-      <c r="AL2" s="71"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="74"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="83"/>
+      <c r="N2" s="83"/>
+      <c r="O2" s="83"/>
+      <c r="P2" s="83"/>
+      <c r="Q2" s="83"/>
+      <c r="R2" s="83"/>
+      <c r="S2" s="83"/>
+      <c r="T2" s="83"/>
+      <c r="U2" s="83"/>
+      <c r="V2" s="83"/>
+      <c r="W2" s="83"/>
+      <c r="X2" s="83"/>
+      <c r="Y2" s="83"/>
+      <c r="Z2" s="83"/>
+      <c r="AA2" s="83"/>
+      <c r="AB2" s="83"/>
+      <c r="AC2" s="83"/>
+      <c r="AD2" s="83"/>
+      <c r="AE2" s="83"/>
+      <c r="AF2" s="83"/>
+      <c r="AG2" s="83"/>
+      <c r="AH2" s="83"/>
+      <c r="AI2" s="84"/>
+      <c r="AJ2" s="86"/>
+      <c r="AK2" s="89"/>
+      <c r="AL2" s="92"/>
     </row>
     <row r="3" spans="1:38" ht="27.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="55"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="57"/>
+      <c r="A3" s="76"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="78"/>
       <c r="D3" s="10" t="s">
         <v>5</v>
       </c>
@@ -1796,9 +2045,9 @@
       <c r="AI3" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="AJ3" s="65"/>
-      <c r="AK3" s="68"/>
-      <c r="AL3" s="71"/>
+      <c r="AJ3" s="86"/>
+      <c r="AK3" s="89"/>
+      <c r="AL3" s="92"/>
     </row>
     <row r="4" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
@@ -1906,9 +2155,9 @@
       <c r="AI4" s="22">
         <v>1</v>
       </c>
-      <c r="AJ4" s="66"/>
-      <c r="AK4" s="69"/>
-      <c r="AL4" s="72"/>
+      <c r="AJ4" s="87"/>
+      <c r="AK4" s="90"/>
+      <c r="AL4" s="93"/>
     </row>
     <row r="5" spans="1:38" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
@@ -3727,11 +3976,11 @@
     <mergeCell ref="AL1:AL4"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:AI20">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="P">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="A">
+      <formula>NOT(ISERROR(SEARCH("A",D5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="P">
       <formula>NOT(ISERROR(SEARCH("P",D5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="A">
-      <formula>NOT(ISERROR(SEARCH("A",D5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3741,17 +3990,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:R169"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="8" width="5.42578125" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" customWidth="1"/>
+    <col min="6" max="6" width="7.7109375" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" customWidth="1"/>
+    <col min="8" max="8" width="5.42578125" customWidth="1"/>
     <col min="9" max="9" width="9.85546875" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -4042,21 +4292,22 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
+      <c r="A18" s="49"/>
+      <c r="B18" s="49" t="s">
         <v>176</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="49" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="A19" s="49" t="s">
         <v>163</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="49" t="s">
         <v>177</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="49" t="s">
         <v>175</v>
       </c>
     </row>
@@ -4294,17 +4545,17 @@
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="79" t="s">
+      <c r="A33" s="49" t="s">
         <v>179</v>
       </c>
-      <c r="D33" s="80" t="s">
+      <c r="D33" s="50" t="s">
         <v>187</v>
       </c>
-      <c r="E33" s="80"/>
-      <c r="F33" s="80"/>
-      <c r="G33" s="80"/>
-      <c r="H33" s="80"/>
-      <c r="I33" s="80"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="50"/>
+      <c r="G33" s="50"/>
+      <c r="H33" s="50"/>
+      <c r="I33" s="50"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="30" t="s">
@@ -4313,14 +4564,14 @@
       <c r="B34" s="30" t="s">
         <v>181</v>
       </c>
-      <c r="C34" s="79"/>
+      <c r="C34" s="49"/>
       <c r="D34" s="1" t="s">
         <v>182</v>
       </c>
       <c r="E34" s="1">
         <v>34</v>
       </c>
-      <c r="F34" s="82" t="str">
+      <c r="F34" s="51" t="str">
         <f>IF(E34&gt;33,D34&amp;" is Pass",D34&amp;" is Fail")</f>
         <v>Anu is Pass</v>
       </c>
@@ -4340,7 +4591,7 @@
       <c r="E35" s="1">
         <v>56</v>
       </c>
-      <c r="F35" s="82" t="str">
+      <c r="F35" s="51" t="str">
         <f t="shared" ref="F35:F38" si="9">IF(E35&gt;33,D35&amp;" is Pass",D35&amp;" is Fail")</f>
         <v>Seema is Pass</v>
       </c>
@@ -4360,7 +4611,7 @@
       <c r="E36" s="1">
         <v>12</v>
       </c>
-      <c r="F36" s="82" t="str">
+      <c r="F36" s="51" t="str">
         <f t="shared" si="9"/>
         <v>Deepak is Fail</v>
       </c>
@@ -4380,7 +4631,7 @@
       <c r="E37" s="1">
         <v>67</v>
       </c>
-      <c r="F37" s="82" t="str">
+      <c r="F37" s="51" t="str">
         <f t="shared" si="9"/>
         <v>Jyoti is Pass</v>
       </c>
@@ -4400,7 +4651,7 @@
       <c r="E38" s="1">
         <v>23</v>
       </c>
-      <c r="F38" s="82" t="str">
+      <c r="F38" s="51" t="str">
         <f t="shared" si="9"/>
         <v>Manav is Fail</v>
       </c>
@@ -4424,306 +4675,2068 @@
         <v/>
       </c>
     </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="35"/>
+      <c r="B41" s="35"/>
+    </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B42" t="s">
+      <c r="A42" s="35"/>
+      <c r="B42" s="35"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="35"/>
+      <c r="B43" s="35"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="35"/>
+      <c r="B44" s="35"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="35"/>
+      <c r="B45" s="35"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B47" s="49" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B43" t="s">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B48" s="49" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B44" t="s">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B49" s="49" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="30" t="s">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="30" t="s">
         <v>189</v>
       </c>
-      <c r="B45" s="30" t="s">
+      <c r="B50" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="C45" s="30" t="s">
+      <c r="C50" s="30" t="s">
         <v>190</v>
       </c>
-      <c r="D45" s="30" t="s">
+      <c r="D50" s="30" t="s">
         <v>191</v>
       </c>
-      <c r="E45" s="30" t="s">
+      <c r="E50" s="30" t="s">
         <v>192</v>
       </c>
-      <c r="F45" s="30" t="s">
+      <c r="F50" s="30" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="26">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="26">
         <v>1</v>
       </c>
-      <c r="B46" s="26" t="s">
+      <c r="B51" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="C46" s="26">
+      <c r="C51" s="26">
         <v>12</v>
       </c>
-      <c r="D46" s="26">
+      <c r="D51" s="26">
         <v>14</v>
       </c>
-      <c r="E46" s="26">
+      <c r="E51" s="26">
         <v>32</v>
       </c>
-      <c r="F46" s="26">
-        <f>SUM(C46,D46,E46)</f>
+      <c r="F51" s="26">
+        <f>SUM(C51,D51,E51)</f>
         <v>58</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="26">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="26">
         <v>2</v>
       </c>
-      <c r="B47" s="26" t="s">
+      <c r="B52" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="C47" s="26">
+      <c r="C52" s="26">
         <v>62</v>
       </c>
-      <c r="D47" s="26">
+      <c r="D52" s="26">
         <v>76</v>
       </c>
-      <c r="E47" s="26">
+      <c r="E52" s="26">
         <v>20</v>
       </c>
-      <c r="F47" s="26">
-        <f t="shared" ref="F47:F50" si="11">SUM(C47,D47,E47)</f>
+      <c r="F52" s="26">
+        <f t="shared" ref="F52:F55" si="11">SUM(C52,D52,E52)</f>
         <v>158</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="26">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="26">
         <v>3</v>
       </c>
-      <c r="B48" s="26" t="s">
+      <c r="B53" s="26" t="s">
         <v>195</v>
       </c>
-      <c r="C48" s="26">
+      <c r="C53" s="26">
         <v>33</v>
       </c>
-      <c r="D48" s="26">
+      <c r="D53" s="26">
         <v>27</v>
       </c>
-      <c r="E48" s="26">
+      <c r="E53" s="26">
         <v>94</v>
       </c>
-      <c r="F48" s="26">
+      <c r="F53" s="26">
         <f t="shared" si="11"/>
         <v>154</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="26">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="26">
         <v>4</v>
       </c>
-      <c r="B49" s="26" t="s">
+      <c r="B54" s="26" t="s">
         <v>184</v>
       </c>
-      <c r="C49" s="26">
-        <v>17</v>
-      </c>
-      <c r="D49" s="26">
+      <c r="C54" s="26">
+        <v>17</v>
+      </c>
+      <c r="D54" s="26">
         <v>95</v>
       </c>
-      <c r="E49" s="26">
+      <c r="E54" s="26">
         <v>74</v>
       </c>
-      <c r="F49" s="26">
+      <c r="F54" s="26">
         <f t="shared" si="11"/>
         <v>186</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="26">
-        <v>5</v>
-      </c>
-      <c r="B50" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="C50" s="26">
-        <v>10</v>
-      </c>
-      <c r="D50" s="26">
-        <v>97</v>
-      </c>
-      <c r="E50" s="26">
-        <v>78</v>
-      </c>
-      <c r="F50" s="26">
-        <f t="shared" si="11"/>
-        <v>185</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B53" s="81" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="B54" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="C54" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="D54" s="30" t="s">
-        <v>191</v>
-      </c>
-      <c r="E54" s="30" t="s">
-        <v>192</v>
-      </c>
-      <c r="F54" s="30" t="s">
-        <v>193</v>
-      </c>
-      <c r="I54" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="J54" s="30" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="26">
         <v>5</v>
       </c>
-      <c r="B55" s="1" t="str">
-        <f>VLOOKUP($A55,$A$46:$F$50,2,0)</f>
+      <c r="B55" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="C55" s="26">
+        <v>10</v>
+      </c>
+      <c r="D55" s="26">
+        <v>97</v>
+      </c>
+      <c r="E55" s="26">
+        <v>78</v>
+      </c>
+      <c r="F55" s="26">
+        <f t="shared" si="11"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="58" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B58" s="56" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="B59" s="55" t="s">
+        <v>2</v>
+      </c>
+      <c r="C59" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="D59" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="E59" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="F59" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="I59" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="J59" s="30" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="26">
+        <v>5</v>
+      </c>
+      <c r="B60" s="1" t="str">
+        <f>VLOOKUP($A60,$A$51:$F$55,2,0)</f>
         <v>Jatin</v>
       </c>
-      <c r="C55" s="1">
-        <f>VLOOKUP($A55,$A$46:$F$50,3,0)</f>
+      <c r="C60" s="1">
+        <f>VLOOKUP($A60,$A$51:$F$55,3,0)</f>
         <v>10</v>
       </c>
-      <c r="D55" s="1">
-        <f>VLOOKUP($A55,$A$46:$F$50,4,0)</f>
+      <c r="D60" s="1">
+        <f>VLOOKUP($A60,$A$51:$F$55,4,0)</f>
         <v>97</v>
       </c>
-      <c r="E55" s="1">
-        <f>VLOOKUP($A55,$A$46:$F$50,5,0)</f>
+      <c r="E60" s="1">
+        <f>VLOOKUP($A60,$A$51:$F$55,5,0)</f>
         <v>78</v>
       </c>
-      <c r="F55" s="1">
-        <f>VLOOKUP($A55,$A$46:$F$50,6,0)</f>
+      <c r="F60" s="1">
+        <f>VLOOKUP($A60,$A$51:$F$55,6,0)</f>
         <v>185</v>
       </c>
-      <c r="I55" s="1" t="s">
+      <c r="I60" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="J55" s="1"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="26">
+      <c r="J60" s="1">
+        <f>VLOOKUP($I60,$B$50:$F$55,5,0)</f>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="26">
         <v>3</v>
       </c>
-      <c r="B56" s="1" t="str">
-        <f t="shared" ref="B56:B58" si="12">VLOOKUP($A56,$A$46:$F$50,2,0)</f>
+      <c r="B61" s="1" t="str">
+        <f t="shared" ref="B61:B63" si="12">VLOOKUP($A61,$A$51:$F$55,2,0)</f>
         <v>Sam</v>
       </c>
-      <c r="C56" s="1">
-        <f t="shared" ref="C56:C58" si="13">VLOOKUP($A56,$A$46:$F$50,3,0)</f>
+      <c r="C61" s="1">
+        <f t="shared" ref="C61:C63" si="13">VLOOKUP($A61,$A$51:$F$55,3,0)</f>
         <v>33</v>
       </c>
-      <c r="D56" s="1">
-        <f t="shared" ref="D56:D58" si="14">VLOOKUP($A56,$A$46:$F$50,4,0)</f>
+      <c r="D61" s="1">
+        <f t="shared" ref="D61:D63" si="14">VLOOKUP($A61,$A$51:$F$55,4,0)</f>
         <v>27</v>
       </c>
-      <c r="E56" s="1">
-        <f t="shared" ref="E56:E58" si="15">VLOOKUP($A56,$A$46:$F$50,5,0)</f>
+      <c r="E61" s="1">
+        <f t="shared" ref="E61:E63" si="15">VLOOKUP($A61,$A$51:$F$55,5,0)</f>
         <v>94</v>
       </c>
-      <c r="F56" s="1">
-        <f t="shared" ref="F56:F58" si="16">VLOOKUP($A56,$A$46:$F$50,6,0)</f>
+      <c r="F61" s="1">
+        <f t="shared" ref="F61:F63" si="16">VLOOKUP($A61,$A$51:$F$55,6,0)</f>
         <v>154</v>
       </c>
-      <c r="I56" s="1" t="s">
+      <c r="I61" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="J56" s="1"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="26">
+      <c r="J61" s="1">
+        <f t="shared" ref="J61:J64" si="17">VLOOKUP($I61,$B$50:$F$55,5,0)</f>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="26">
         <v>2</v>
       </c>
-      <c r="B57" s="1" t="str">
+      <c r="B62" s="1" t="str">
         <f t="shared" si="12"/>
         <v>Seema</v>
       </c>
-      <c r="C57" s="1">
+      <c r="C62" s="1">
         <f t="shared" si="13"/>
         <v>62</v>
       </c>
-      <c r="D57" s="1">
+      <c r="D62" s="1">
         <f t="shared" si="14"/>
         <v>76</v>
       </c>
-      <c r="E57" s="1">
+      <c r="E62" s="1">
         <f t="shared" si="15"/>
         <v>20</v>
       </c>
-      <c r="F57" s="1">
+      <c r="F62" s="1">
         <f t="shared" si="16"/>
         <v>158</v>
       </c>
-      <c r="I57" s="1" t="s">
+      <c r="I62" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="J57" s="1"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="26">
+      <c r="J62" s="1">
+        <f t="shared" si="17"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="26">
         <v>1</v>
       </c>
-      <c r="B58" s="1" t="str">
+      <c r="B63" s="1" t="str">
         <f t="shared" si="12"/>
         <v>Anu</v>
       </c>
-      <c r="C58" s="1">
+      <c r="C63" s="1">
         <f t="shared" si="13"/>
         <v>12</v>
       </c>
-      <c r="D58" s="1">
+      <c r="D63" s="1">
         <f t="shared" si="14"/>
         <v>14</v>
       </c>
-      <c r="E58" s="1">
+      <c r="E63" s="1">
         <f t="shared" si="15"/>
         <v>32</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F63" s="1">
         <f t="shared" si="16"/>
         <v>58</v>
       </c>
-      <c r="I58" s="1" t="s">
+      <c r="I63" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="J58" s="1"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="I59" s="1" t="s">
+      <c r="J63" s="1">
+        <f t="shared" si="17"/>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I64" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="J59" s="1"/>
+      <c r="J64" s="1">
+        <f t="shared" si="17"/>
+        <v>158</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A66" s="31"/>
+      <c r="B66" s="32"/>
+      <c r="C66" s="32"/>
+      <c r="D66" s="33"/>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A67" s="34"/>
+      <c r="B67" s="65" t="s">
+        <v>199</v>
+      </c>
+      <c r="C67" s="35"/>
+      <c r="D67" s="36"/>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A68" s="34"/>
+      <c r="B68" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="C68" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="D68" s="36"/>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A69" s="34"/>
+      <c r="B69" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="C69" s="1">
+        <f>VLOOKUP(TRIM($B69),$B$50:$F$55,5,0)</f>
+        <v>58</v>
+      </c>
+      <c r="D69" s="36"/>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A70" s="34"/>
+      <c r="B70" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="C70" s="1">
+        <f t="shared" ref="C70:C73" si="18">VLOOKUP(TRIM($B70),$B$50:$F$55,5,0)</f>
+        <v>185</v>
+      </c>
+      <c r="D70" s="36"/>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A71" s="34"/>
+      <c r="B71" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C71" s="1">
+        <f t="shared" si="18"/>
+        <v>186</v>
+      </c>
+      <c r="D71" s="36"/>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A72" s="34"/>
+      <c r="B72" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C72" s="1">
+        <f t="shared" si="18"/>
+        <v>154</v>
+      </c>
+      <c r="D72" s="36"/>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A73" s="34"/>
+      <c r="B73" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C73" s="1">
+        <f t="shared" si="18"/>
+        <v>158</v>
+      </c>
+      <c r="D73" s="36"/>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A74" s="34"/>
+      <c r="B74" s="35"/>
+      <c r="C74" s="35"/>
+      <c r="D74" s="36"/>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A75" s="34"/>
+      <c r="B75" s="35"/>
+      <c r="C75" s="35"/>
+      <c r="D75" s="36"/>
+    </row>
+    <row r="76" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="37"/>
+      <c r="B76" s="38"/>
+      <c r="C76" s="38"/>
+      <c r="D76" s="39"/>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="K77" s="31"/>
+      <c r="L77" s="32"/>
+      <c r="M77" s="32"/>
+      <c r="N77" s="32"/>
+      <c r="O77" s="32"/>
+      <c r="P77" s="32"/>
+      <c r="Q77" s="32"/>
+      <c r="R77" s="33"/>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="K78" s="34"/>
+      <c r="L78" s="35" t="s">
+        <v>206</v>
+      </c>
+      <c r="M78" s="35"/>
+      <c r="N78" s="35"/>
+      <c r="O78" s="35"/>
+      <c r="P78" s="35"/>
+      <c r="Q78" s="35"/>
+      <c r="R78" s="36"/>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A79" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="B79" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="C79" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="D79" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="E79" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="F79" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="K79" s="34"/>
+      <c r="L79" s="52" t="s">
+        <v>189</v>
+      </c>
+      <c r="M79" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="N79" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="O79" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="P79" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q79" s="53" t="s">
+        <v>193</v>
+      </c>
+      <c r="R79" s="36"/>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A80" s="26">
+        <v>1</v>
+      </c>
+      <c r="B80" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="C80" s="26">
+        <v>12</v>
+      </c>
+      <c r="D80" s="26">
+        <v>14</v>
+      </c>
+      <c r="E80" s="26">
+        <v>32</v>
+      </c>
+      <c r="F80" s="26">
+        <f>SUM(C80,D80,E80)</f>
+        <v>58</v>
+      </c>
+      <c r="K80" s="34"/>
+      <c r="L80" s="54">
+        <v>5</v>
+      </c>
+      <c r="M80" s="1" t="str">
+        <f t="shared" ref="M80:Q83" si="19">VLOOKUP($L80,result,COLUMN()-11,0)</f>
+        <v>Jatin</v>
+      </c>
+      <c r="N80" s="1">
+        <f t="shared" si="19"/>
+        <v>10</v>
+      </c>
+      <c r="O80" s="1">
+        <f t="shared" si="19"/>
+        <v>97</v>
+      </c>
+      <c r="P80" s="1">
+        <f t="shared" si="19"/>
+        <v>78</v>
+      </c>
+      <c r="Q80" s="1">
+        <f t="shared" si="19"/>
+        <v>185</v>
+      </c>
+      <c r="R80" s="36"/>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A81" s="26">
+        <v>2</v>
+      </c>
+      <c r="B81" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="C81" s="26">
+        <v>62</v>
+      </c>
+      <c r="D81" s="26">
+        <v>76</v>
+      </c>
+      <c r="E81" s="26">
+        <v>20</v>
+      </c>
+      <c r="F81" s="26">
+        <f t="shared" ref="F81:F84" si="20">SUM(C81,D81,E81)</f>
+        <v>158</v>
+      </c>
+      <c r="K81" s="34"/>
+      <c r="L81" s="54">
+        <v>3</v>
+      </c>
+      <c r="M81" s="1" t="str">
+        <f t="shared" si="19"/>
+        <v>Sam</v>
+      </c>
+      <c r="N81" s="1">
+        <f t="shared" si="19"/>
+        <v>33</v>
+      </c>
+      <c r="O81" s="1">
+        <f t="shared" si="19"/>
+        <v>27</v>
+      </c>
+      <c r="P81" s="1">
+        <f t="shared" si="19"/>
+        <v>94</v>
+      </c>
+      <c r="Q81" s="1">
+        <f t="shared" si="19"/>
+        <v>154</v>
+      </c>
+      <c r="R81" s="36"/>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A82" s="26">
+        <v>3</v>
+      </c>
+      <c r="B82" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="C82" s="26">
+        <v>33</v>
+      </c>
+      <c r="D82" s="26">
+        <v>27</v>
+      </c>
+      <c r="E82" s="26">
+        <v>94</v>
+      </c>
+      <c r="F82" s="26">
+        <f t="shared" si="20"/>
+        <v>154</v>
+      </c>
+      <c r="K82" s="34"/>
+      <c r="L82" s="54">
+        <v>2</v>
+      </c>
+      <c r="M82" s="1" t="str">
+        <f t="shared" si="19"/>
+        <v>Seema</v>
+      </c>
+      <c r="N82" s="1">
+        <f t="shared" si="19"/>
+        <v>62</v>
+      </c>
+      <c r="O82" s="1">
+        <f t="shared" si="19"/>
+        <v>76</v>
+      </c>
+      <c r="P82" s="1">
+        <f t="shared" si="19"/>
+        <v>20</v>
+      </c>
+      <c r="Q82" s="1">
+        <f t="shared" si="19"/>
+        <v>158</v>
+      </c>
+      <c r="R82" s="36"/>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A83" s="26">
+        <v>4</v>
+      </c>
+      <c r="B83" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="C83" s="26">
+        <v>17</v>
+      </c>
+      <c r="D83" s="26">
+        <v>95</v>
+      </c>
+      <c r="E83" s="26">
+        <v>74</v>
+      </c>
+      <c r="F83" s="26">
+        <f t="shared" si="20"/>
+        <v>186</v>
+      </c>
+      <c r="K83" s="34"/>
+      <c r="L83" s="54">
+        <v>1</v>
+      </c>
+      <c r="M83" s="1" t="str">
+        <f t="shared" si="19"/>
+        <v>Anu</v>
+      </c>
+      <c r="N83" s="1">
+        <f t="shared" si="19"/>
+        <v>12</v>
+      </c>
+      <c r="O83" s="1">
+        <f t="shared" si="19"/>
+        <v>14</v>
+      </c>
+      <c r="P83" s="1">
+        <f t="shared" si="19"/>
+        <v>32</v>
+      </c>
+      <c r="Q83" s="1">
+        <f t="shared" si="19"/>
+        <v>58</v>
+      </c>
+      <c r="R83" s="36"/>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A84" s="26">
+        <v>5</v>
+      </c>
+      <c r="B84" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="C84" s="26">
+        <v>10</v>
+      </c>
+      <c r="D84" s="26">
+        <v>97</v>
+      </c>
+      <c r="E84" s="26">
+        <v>78</v>
+      </c>
+      <c r="F84" s="26">
+        <f t="shared" si="20"/>
+        <v>185</v>
+      </c>
+      <c r="K84" s="34"/>
+      <c r="L84" s="35"/>
+      <c r="M84" s="35"/>
+      <c r="N84" s="35"/>
+      <c r="O84" s="35"/>
+      <c r="P84" s="35"/>
+      <c r="Q84" s="35"/>
+      <c r="R84" s="36"/>
+    </row>
+    <row r="85" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K85" s="34"/>
+      <c r="L85" s="35"/>
+      <c r="M85" s="35">
+        <f>COLUMN()</f>
+        <v>13</v>
+      </c>
+      <c r="N85" s="35"/>
+      <c r="O85" s="35"/>
+      <c r="P85" s="35"/>
+      <c r="Q85" s="35"/>
+      <c r="R85" s="36"/>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A86" s="31"/>
+      <c r="B86" s="32"/>
+      <c r="C86" s="32"/>
+      <c r="D86" s="32"/>
+      <c r="E86" s="32"/>
+      <c r="F86" s="33"/>
+      <c r="K86" s="34"/>
+      <c r="L86" s="35"/>
+      <c r="M86" s="35"/>
+      <c r="N86" s="35"/>
+      <c r="O86" s="35"/>
+      <c r="P86" s="35"/>
+      <c r="Q86" s="35"/>
+      <c r="R86" s="36"/>
+    </row>
+    <row r="87" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="34"/>
+      <c r="B87" s="59" t="s">
+        <v>205</v>
+      </c>
+      <c r="C87" s="35"/>
+      <c r="D87" s="35"/>
+      <c r="E87" s="35"/>
+      <c r="F87" s="36"/>
+      <c r="K87" s="37"/>
+      <c r="L87" s="38"/>
+      <c r="M87" s="38"/>
+      <c r="N87" s="38"/>
+      <c r="O87" s="38"/>
+      <c r="P87" s="38"/>
+      <c r="Q87" s="38"/>
+      <c r="R87" s="39"/>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A88" s="52" t="s">
+        <v>189</v>
+      </c>
+      <c r="B88" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="C88" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="D88" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="E88" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="F88" s="53" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A89" s="54">
+        <v>5</v>
+      </c>
+      <c r="B89" s="1" t="str">
+        <f>VLOOKUP($A89,result,2,0)</f>
+        <v>Jatin</v>
+      </c>
+      <c r="C89" s="1">
+        <f>VLOOKUP($A89,result,3,0)</f>
+        <v>10</v>
+      </c>
+      <c r="D89" s="1">
+        <f>VLOOKUP($A89,result,4,0)</f>
+        <v>97</v>
+      </c>
+      <c r="E89" s="1">
+        <f>VLOOKUP($A89,result,5,0)</f>
+        <v>78</v>
+      </c>
+      <c r="F89" s="6">
+        <f>VLOOKUP($A89,result,6,0)</f>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A90" s="54">
+        <v>3</v>
+      </c>
+      <c r="B90" s="1" t="str">
+        <f>VLOOKUP($A90,result,2,0)</f>
+        <v>Sam</v>
+      </c>
+      <c r="C90" s="1">
+        <f>VLOOKUP($A90,result,3,0)</f>
+        <v>33</v>
+      </c>
+      <c r="D90" s="1">
+        <f>VLOOKUP($A90,result,4,0)</f>
+        <v>27</v>
+      </c>
+      <c r="E90" s="1">
+        <f>VLOOKUP($A90,result,5,0)</f>
+        <v>94</v>
+      </c>
+      <c r="F90" s="6">
+        <f>VLOOKUP($A90,result,6,0)</f>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A91" s="54">
+        <v>2</v>
+      </c>
+      <c r="B91" s="1" t="str">
+        <f>VLOOKUP($A91,result,2,0)</f>
+        <v>Seema</v>
+      </c>
+      <c r="C91" s="1">
+        <f>VLOOKUP($A91,result,3,0)</f>
+        <v>62</v>
+      </c>
+      <c r="D91" s="1">
+        <f>VLOOKUP($A91,result,4,0)</f>
+        <v>76</v>
+      </c>
+      <c r="E91" s="1">
+        <f>VLOOKUP($A91,result,5,0)</f>
+        <v>20</v>
+      </c>
+      <c r="F91" s="6">
+        <f>VLOOKUP($A91,result,6,0)</f>
+        <v>158</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A92" s="54">
+        <v>1</v>
+      </c>
+      <c r="B92" s="1" t="str">
+        <f>VLOOKUP($A92,result,2,0)</f>
+        <v>Anu</v>
+      </c>
+      <c r="C92" s="1">
+        <f>VLOOKUP($A92,result,3,0)</f>
+        <v>12</v>
+      </c>
+      <c r="D92" s="1">
+        <f>VLOOKUP($A92,result,4,0)</f>
+        <v>14</v>
+      </c>
+      <c r="E92" s="1">
+        <f>VLOOKUP($A92,result,5,0)</f>
+        <v>32</v>
+      </c>
+      <c r="F92" s="6">
+        <f>VLOOKUP($A92,result,6,0)</f>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A93" s="34"/>
+      <c r="B93" s="35"/>
+      <c r="C93" s="35"/>
+      <c r="D93" s="35"/>
+      <c r="E93" s="35"/>
+      <c r="F93" s="36"/>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A94" s="34"/>
+      <c r="B94" s="35"/>
+      <c r="C94" s="35"/>
+      <c r="D94" s="35"/>
+      <c r="E94" s="35"/>
+      <c r="F94" s="36"/>
+    </row>
+    <row r="95" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="37"/>
+      <c r="B95" s="38"/>
+      <c r="C95" s="38"/>
+      <c r="D95" s="38"/>
+      <c r="E95" s="38"/>
+      <c r="F95" s="39"/>
+    </row>
+    <row r="97" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="31"/>
+      <c r="B98" s="32"/>
+      <c r="C98" s="32"/>
+      <c r="D98" s="32"/>
+      <c r="E98" s="32"/>
+      <c r="F98" s="33"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="34"/>
+      <c r="B99" s="65" t="s">
+        <v>207</v>
+      </c>
+      <c r="C99" s="35"/>
+      <c r="D99" s="35"/>
+      <c r="E99" s="35"/>
+      <c r="F99" s="36"/>
+    </row>
+    <row r="100" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A100" s="60" t="s">
+        <v>208</v>
+      </c>
+      <c r="B100" s="30" t="s">
+        <v>216</v>
+      </c>
+      <c r="C100" s="35"/>
+      <c r="D100" s="60" t="s">
+        <v>210</v>
+      </c>
+      <c r="E100" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="F100" s="36"/>
+    </row>
+    <row r="101" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A101" s="63">
+        <v>1</v>
+      </c>
+      <c r="B101" s="1" t="str">
+        <f>VLOOKUP($A101,$D$101:$E$105,2,1)</f>
+        <v>Poor</v>
+      </c>
+      <c r="C101" s="35" t="s">
+        <v>217</v>
+      </c>
+      <c r="D101" s="61">
+        <v>0</v>
+      </c>
+      <c r="E101" s="62" t="s">
+        <v>211</v>
+      </c>
+      <c r="F101" s="36"/>
+    </row>
+    <row r="102" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A102" s="63">
+        <v>30</v>
+      </c>
+      <c r="B102" s="1" t="str">
+        <f t="shared" ref="B102:B106" si="21">VLOOKUP($A102,$D$101:$E$105,2,1)</f>
+        <v>Poor</v>
+      </c>
+      <c r="C102" s="35" t="s">
+        <v>218</v>
+      </c>
+      <c r="D102" s="61">
+        <v>35</v>
+      </c>
+      <c r="E102" s="62" t="s">
+        <v>212</v>
+      </c>
+      <c r="F102" s="36"/>
+    </row>
+    <row r="103" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A103" s="63">
+        <v>50</v>
+      </c>
+      <c r="B103" s="1" t="str">
+        <f t="shared" si="21"/>
+        <v xml:space="preserve"> Avg</v>
+      </c>
+      <c r="C103" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="D103" s="61">
+        <v>60</v>
+      </c>
+      <c r="E103" s="62" t="s">
+        <v>213</v>
+      </c>
+      <c r="F103" s="36"/>
+    </row>
+    <row r="104" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A104" s="63">
+        <v>70</v>
+      </c>
+      <c r="B104" s="1" t="str">
+        <f t="shared" si="21"/>
+        <v>Good</v>
+      </c>
+      <c r="C104" s="58" t="s">
+        <v>220</v>
+      </c>
+      <c r="D104" s="61">
+        <v>80</v>
+      </c>
+      <c r="E104" s="62" t="s">
+        <v>214</v>
+      </c>
+      <c r="F104" s="36"/>
+    </row>
+    <row r="105" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A105" s="63">
+        <v>85</v>
+      </c>
+      <c r="B105" s="1" t="str">
+        <f t="shared" si="21"/>
+        <v>Best</v>
+      </c>
+      <c r="C105" s="58" t="s">
+        <v>221</v>
+      </c>
+      <c r="D105" s="61">
+        <v>90</v>
+      </c>
+      <c r="E105" s="62" t="s">
+        <v>215</v>
+      </c>
+      <c r="F105" s="36"/>
+    </row>
+    <row r="106" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A106" s="63">
+        <v>100</v>
+      </c>
+      <c r="B106" s="1" t="str">
+        <f t="shared" si="21"/>
+        <v>Sup</v>
+      </c>
+      <c r="C106" s="35"/>
+      <c r="D106" s="64"/>
+      <c r="E106" s="64"/>
+      <c r="F106" s="36"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="34"/>
+      <c r="B107" s="35"/>
+      <c r="C107" s="35"/>
+      <c r="D107" s="35"/>
+      <c r="E107" s="35"/>
+      <c r="F107" s="36"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="34"/>
+      <c r="B108" s="35"/>
+      <c r="C108" s="35"/>
+      <c r="D108" s="35"/>
+      <c r="E108" s="35"/>
+      <c r="F108" s="36"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="34"/>
+      <c r="B109" s="35"/>
+      <c r="C109" s="35"/>
+      <c r="D109" s="35"/>
+      <c r="E109" s="35"/>
+      <c r="F109" s="36"/>
+    </row>
+    <row r="110" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="37"/>
+      <c r="B110" s="38"/>
+      <c r="C110" s="38"/>
+      <c r="D110" s="38"/>
+      <c r="E110" s="38"/>
+      <c r="F110" s="39"/>
+    </row>
+    <row r="111" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="31"/>
+      <c r="B112" s="32"/>
+      <c r="C112" s="32"/>
+      <c r="D112" s="33"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="34"/>
+      <c r="B113" s="65" t="s">
+        <v>230</v>
+      </c>
+      <c r="C113" s="35"/>
+      <c r="D113" s="36"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="34"/>
+      <c r="B114" s="35"/>
+      <c r="C114" s="35"/>
+      <c r="D114" s="36"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="34"/>
+      <c r="B115" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="C115" s="30" t="s">
+        <v>223</v>
+      </c>
+      <c r="D115" s="36"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="34"/>
+      <c r="B116" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="C116" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="D116" s="36"/>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="34"/>
+      <c r="B117" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="C117" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="D117" s="36"/>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" s="34"/>
+      <c r="B118" s="35"/>
+      <c r="C118" s="35"/>
+      <c r="D118" s="36"/>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" s="34"/>
+      <c r="B119" s="35"/>
+      <c r="C119" s="35"/>
+      <c r="D119" s="36"/>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" s="34"/>
+      <c r="B120" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="C120" s="30" t="s">
+        <v>223</v>
+      </c>
+      <c r="D120" s="36"/>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" s="34"/>
+      <c r="B121" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="C121" s="29" t="str">
+        <f>IFERROR(VLOOKUP($B121&amp;"*",$B$116:$C$117,2,0),"")</f>
+        <v>Gurugram</v>
+      </c>
+      <c r="D121" s="36"/>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" s="34"/>
+      <c r="B122" s="26" t="s">
+        <v>226</v>
+      </c>
+      <c r="C122" s="29" t="str">
+        <f t="shared" ref="C122:C123" si="22">IFERROR(VLOOKUP($B122&amp;"*",$B$116:$C$117,2,0),"")</f>
+        <v>Delhi</v>
+      </c>
+      <c r="D122" s="36"/>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" s="34"/>
+      <c r="B123" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="C123" s="29" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="D123" s="36"/>
+    </row>
+    <row r="124" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="37"/>
+      <c r="B124" s="38"/>
+      <c r="C124" s="38"/>
+      <c r="D124" s="39"/>
+    </row>
+    <row r="125" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" s="31"/>
+      <c r="B126" s="32"/>
+      <c r="C126" s="32"/>
+      <c r="D126" s="32"/>
+      <c r="E126" s="32"/>
+      <c r="F126" s="32"/>
+      <c r="G126" s="32"/>
+      <c r="H126" s="33"/>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" s="34"/>
+      <c r="B127" s="65" t="s">
+        <v>238</v>
+      </c>
+      <c r="C127" s="35"/>
+      <c r="D127" s="35"/>
+      <c r="E127" s="35"/>
+      <c r="F127" s="35"/>
+      <c r="G127" s="35"/>
+      <c r="H127" s="36"/>
+    </row>
+    <row r="128" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A128" s="66"/>
+      <c r="B128" s="35"/>
+      <c r="C128" s="35"/>
+      <c r="D128" s="35"/>
+      <c r="E128" s="35"/>
+      <c r="F128" s="35"/>
+      <c r="G128" s="35"/>
+      <c r="H128" s="36"/>
+    </row>
+    <row r="129" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A129" s="67" t="s">
+        <v>189</v>
+      </c>
+      <c r="B129" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="C129" s="30" t="s">
+        <v>231</v>
+      </c>
+      <c r="D129" s="35"/>
+      <c r="E129" s="35"/>
+      <c r="F129" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="G129" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="H129" s="36"/>
+    </row>
+    <row r="130" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A130" s="68">
+        <v>1</v>
+      </c>
+      <c r="B130" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="C130" s="26">
+        <v>34</v>
+      </c>
+      <c r="D130" s="35"/>
+      <c r="E130" s="35"/>
+      <c r="F130" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="G130" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H130" s="36"/>
+    </row>
+    <row r="131" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A131" s="68">
+        <v>2</v>
+      </c>
+      <c r="B131" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="C131" s="26">
+        <v>54</v>
+      </c>
+      <c r="D131" s="35"/>
+      <c r="E131" s="35"/>
+      <c r="F131" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="G131" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="H131" s="36"/>
+    </row>
+    <row r="132" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A132" s="68">
+        <v>3</v>
+      </c>
+      <c r="B132" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="C132" s="26">
+        <v>67</v>
+      </c>
+      <c r="D132" s="35"/>
+      <c r="E132" s="35"/>
+      <c r="F132" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="G132" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="H132" s="36"/>
+    </row>
+    <row r="133" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A133" s="68">
+        <v>4</v>
+      </c>
+      <c r="B133" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="C133" s="26">
+        <v>87</v>
+      </c>
+      <c r="D133" s="35"/>
+      <c r="E133" s="35"/>
+      <c r="F133" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="G133" s="26" t="s">
+        <v>237</v>
+      </c>
+      <c r="H133" s="36"/>
+    </row>
+    <row r="134" spans="1:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A134" s="68">
+        <v>5</v>
+      </c>
+      <c r="B134" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="C134" s="26">
+        <v>32</v>
+      </c>
+      <c r="D134" s="35"/>
+      <c r="E134" s="35"/>
+      <c r="F134" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="G134" s="26" t="s">
+        <v>235</v>
+      </c>
+      <c r="H134" s="36"/>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" s="34"/>
+      <c r="B135" s="35"/>
+      <c r="C135" s="35"/>
+      <c r="D135" s="35"/>
+      <c r="E135" s="35"/>
+      <c r="F135" s="35"/>
+      <c r="G135" s="35"/>
+      <c r="H135" s="36"/>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" s="34"/>
+      <c r="B136" s="35"/>
+      <c r="C136" s="35"/>
+      <c r="D136" s="35"/>
+      <c r="E136" s="35"/>
+      <c r="F136" s="35"/>
+      <c r="G136" s="35"/>
+      <c r="H136" s="36"/>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" s="34"/>
+      <c r="B137" s="35"/>
+      <c r="C137" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="D137" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="E137" s="35"/>
+      <c r="F137" s="35"/>
+      <c r="G137" s="35"/>
+      <c r="H137" s="36"/>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" s="34"/>
+      <c r="B138" s="35"/>
+      <c r="C138" s="1">
+        <v>5</v>
+      </c>
+      <c r="D138" s="1" t="str">
+        <f>VLOOKUP(VLOOKUP($C138,$A$130:$B$134,2,0),$F$130:$G$134,2,0)</f>
+        <v>Kolkata</v>
+      </c>
+      <c r="E138" s="35"/>
+      <c r="F138" s="35"/>
+      <c r="G138" s="35"/>
+      <c r="H138" s="36"/>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" s="34"/>
+      <c r="B139" s="35"/>
+      <c r="C139" s="1">
+        <v>4</v>
+      </c>
+      <c r="D139" s="1" t="str">
+        <f t="shared" ref="D139:D141" si="23">VLOOKUP(VLOOKUP($C139,$A$130:$B$134,2,0),$F$130:$G$134,2,0)</f>
+        <v>Mumbai</v>
+      </c>
+      <c r="E139" s="35"/>
+      <c r="F139" s="35"/>
+      <c r="G139" s="35"/>
+      <c r="H139" s="36"/>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" s="34"/>
+      <c r="B140" s="35"/>
+      <c r="C140" s="1">
+        <v>2</v>
+      </c>
+      <c r="D140" s="1" t="str">
+        <f t="shared" si="23"/>
+        <v>Noida</v>
+      </c>
+      <c r="E140" s="35"/>
+      <c r="F140" s="35"/>
+      <c r="G140" s="35"/>
+      <c r="H140" s="36"/>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" s="34"/>
+      <c r="B141" s="35"/>
+      <c r="C141" s="1">
+        <v>1</v>
+      </c>
+      <c r="D141" s="1" t="str">
+        <f t="shared" si="23"/>
+        <v>Delhi</v>
+      </c>
+      <c r="E141" s="35"/>
+      <c r="F141" s="35"/>
+      <c r="G141" s="35"/>
+      <c r="H141" s="36"/>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" s="34"/>
+      <c r="B142" s="35"/>
+      <c r="C142" s="35"/>
+      <c r="D142" s="35"/>
+      <c r="E142" s="35"/>
+      <c r="F142" s="35"/>
+      <c r="G142" s="35"/>
+      <c r="H142" s="36"/>
+    </row>
+    <row r="143" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="37"/>
+      <c r="B143" s="38"/>
+      <c r="C143" s="38"/>
+      <c r="D143" s="38"/>
+      <c r="E143" s="38"/>
+      <c r="F143" s="38"/>
+      <c r="G143" s="38"/>
+      <c r="H143" s="39"/>
+    </row>
+    <row r="145" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A146" s="31"/>
+      <c r="B146" s="32"/>
+      <c r="C146" s="32"/>
+      <c r="D146" s="32"/>
+      <c r="E146" s="32"/>
+      <c r="F146" s="32"/>
+      <c r="G146" s="32"/>
+      <c r="H146" s="32"/>
+      <c r="I146" s="32"/>
+      <c r="J146" s="32"/>
+      <c r="K146" s="32"/>
+      <c r="L146" s="33"/>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A147" s="34"/>
+      <c r="B147" s="35" t="s">
+        <v>239</v>
+      </c>
+      <c r="C147" s="35"/>
+      <c r="D147" s="35"/>
+      <c r="E147" s="35"/>
+      <c r="F147" s="35"/>
+      <c r="G147" s="35"/>
+      <c r="H147" s="35"/>
+      <c r="I147" s="35"/>
+      <c r="J147" s="35"/>
+      <c r="K147" s="35"/>
+      <c r="L147" s="36"/>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A148" s="34"/>
+      <c r="B148" s="35"/>
+      <c r="C148" s="35"/>
+      <c r="D148" s="35"/>
+      <c r="E148" s="35"/>
+      <c r="F148" s="35"/>
+      <c r="G148" s="35"/>
+      <c r="H148" s="35"/>
+      <c r="I148" s="35"/>
+      <c r="J148" s="35"/>
+      <c r="K148" s="35"/>
+      <c r="L148" s="36"/>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A149" s="34"/>
+      <c r="B149" s="35"/>
+      <c r="C149" s="35"/>
+      <c r="D149" s="35"/>
+      <c r="E149" s="35"/>
+      <c r="F149" s="35"/>
+      <c r="G149" s="35"/>
+      <c r="H149" s="35"/>
+      <c r="I149" s="35"/>
+      <c r="J149" s="35"/>
+      <c r="K149" s="35"/>
+      <c r="L149" s="36"/>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A150" s="52" t="s">
+        <v>240</v>
+      </c>
+      <c r="B150" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="C150" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="D150" s="35"/>
+      <c r="E150" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="F150" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="G150" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="H150" s="35"/>
+      <c r="I150" s="35"/>
+      <c r="J150" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="K150" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="L150" s="53" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A151" s="54">
+        <v>1</v>
+      </c>
+      <c r="B151" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="C151" s="26">
+        <v>10</v>
+      </c>
+      <c r="D151" s="35"/>
+      <c r="E151" s="26">
+        <v>6</v>
+      </c>
+      <c r="F151" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="G151" s="26">
+        <v>60</v>
+      </c>
+      <c r="H151" s="35"/>
+      <c r="I151" s="35"/>
+      <c r="J151" s="26">
+        <v>11</v>
+      </c>
+      <c r="K151" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="L151" s="69">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A152" s="54">
+        <v>2</v>
+      </c>
+      <c r="B152" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="C152" s="26">
+        <v>20</v>
+      </c>
+      <c r="D152" s="35"/>
+      <c r="E152" s="26">
+        <v>7</v>
+      </c>
+      <c r="F152" s="26" t="s">
+        <v>247</v>
+      </c>
+      <c r="G152" s="26">
+        <v>70</v>
+      </c>
+      <c r="H152" s="35"/>
+      <c r="I152" s="35"/>
+      <c r="J152" s="26">
+        <v>12</v>
+      </c>
+      <c r="K152" s="26" t="s">
+        <v>258</v>
+      </c>
+      <c r="L152" s="69">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A153" s="54">
+        <v>3</v>
+      </c>
+      <c r="B153" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="C153" s="26">
+        <v>30</v>
+      </c>
+      <c r="D153" s="35"/>
+      <c r="E153" s="26">
+        <v>8</v>
+      </c>
+      <c r="F153" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="G153" s="26">
+        <v>80</v>
+      </c>
+      <c r="H153" s="35"/>
+      <c r="I153" s="35"/>
+      <c r="J153" s="26">
+        <v>13</v>
+      </c>
+      <c r="K153" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="L153" s="69">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A154" s="54">
+        <v>4</v>
+      </c>
+      <c r="B154" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="C154" s="26">
+        <v>40</v>
+      </c>
+      <c r="D154" s="35"/>
+      <c r="E154" s="26">
+        <v>9</v>
+      </c>
+      <c r="F154" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="G154" s="26">
+        <v>90</v>
+      </c>
+      <c r="H154" s="35"/>
+      <c r="I154" s="35"/>
+      <c r="J154" s="26">
+        <v>14</v>
+      </c>
+      <c r="K154" s="26" t="s">
+        <v>255</v>
+      </c>
+      <c r="L154" s="69">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A155" s="54">
+        <v>5</v>
+      </c>
+      <c r="B155" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="C155" s="26">
+        <v>50</v>
+      </c>
+      <c r="D155" s="35"/>
+      <c r="E155" s="26">
+        <v>10</v>
+      </c>
+      <c r="F155" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="G155" s="26">
+        <v>100</v>
+      </c>
+      <c r="H155" s="35"/>
+      <c r="I155" s="35"/>
+      <c r="J155" s="26">
+        <v>15</v>
+      </c>
+      <c r="K155" s="26" t="s">
+        <v>254</v>
+      </c>
+      <c r="L155" s="69">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A156" s="34"/>
+      <c r="B156" s="35"/>
+      <c r="C156" s="35"/>
+      <c r="D156" s="35"/>
+      <c r="E156" s="35"/>
+      <c r="F156" s="35"/>
+      <c r="G156" s="35"/>
+      <c r="H156" s="35"/>
+      <c r="I156" s="35"/>
+      <c r="J156" s="35"/>
+      <c r="K156" s="35"/>
+      <c r="L156" s="36"/>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A157" s="34"/>
+      <c r="B157" s="35"/>
+      <c r="C157" s="35"/>
+      <c r="D157" s="35"/>
+      <c r="E157" s="35"/>
+      <c r="F157" s="35"/>
+      <c r="G157" s="35"/>
+      <c r="H157" s="35"/>
+      <c r="I157" s="35"/>
+      <c r="J157" s="35"/>
+      <c r="K157" s="35"/>
+      <c r="L157" s="36"/>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A158" s="52" t="s">
+        <v>240</v>
+      </c>
+      <c r="B158" s="1">
+        <v>7</v>
+      </c>
+      <c r="C158" s="35" t="s">
+        <v>253</v>
+      </c>
+      <c r="D158" s="35"/>
+      <c r="E158" s="35"/>
+      <c r="F158" s="35"/>
+      <c r="G158" s="35"/>
+      <c r="H158" s="35"/>
+      <c r="I158" s="35"/>
+      <c r="J158" s="35"/>
+      <c r="K158" s="35"/>
+      <c r="L158" s="36"/>
+    </row>
+    <row r="159" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A159" s="52" t="s">
+        <v>245</v>
+      </c>
+      <c r="B159" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="C159" s="35"/>
+      <c r="D159" s="35"/>
+      <c r="E159" s="35" t="s">
+        <v>251</v>
+      </c>
+      <c r="F159" s="35"/>
+      <c r="G159" s="35"/>
+      <c r="H159" s="35"/>
+      <c r="I159" s="35"/>
+      <c r="J159" s="35"/>
+      <c r="K159" s="35"/>
+      <c r="L159" s="36"/>
+      <c r="M159" s="57"/>
+    </row>
+    <row r="160" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A160" s="5" t="str">
+        <f>VLOOKUP($B$158,IF($B$158&gt;=6,BillNo2,BillNo1),COLUMN()+1,0)</f>
+        <v>Table</v>
+      </c>
+      <c r="B160" s="1">
+        <f>VLOOKUP($B$158,IF($B$158&gt;=6,BillNo2,BillNo1),COLUMN()+1,0)</f>
+        <v>70</v>
+      </c>
+      <c r="C160" s="35"/>
+      <c r="D160" s="35"/>
+      <c r="E160" s="35"/>
+      <c r="F160" s="35"/>
+      <c r="G160" s="35"/>
+      <c r="H160" s="35"/>
+      <c r="I160" s="35"/>
+      <c r="J160" s="35"/>
+      <c r="K160" s="35"/>
+      <c r="L160" s="36"/>
+      <c r="M160" s="57"/>
+    </row>
+    <row r="161" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A161" s="34"/>
+      <c r="B161" s="35"/>
+      <c r="C161" s="35"/>
+      <c r="D161" s="35"/>
+      <c r="E161" s="35"/>
+      <c r="F161" s="35"/>
+      <c r="G161" s="35"/>
+      <c r="H161" s="35"/>
+      <c r="I161" s="35"/>
+      <c r="J161" s="35"/>
+      <c r="K161" s="35"/>
+      <c r="L161" s="36"/>
+      <c r="M161" s="57"/>
+    </row>
+    <row r="162" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A162" s="34"/>
+      <c r="B162" s="35"/>
+      <c r="C162" s="35"/>
+      <c r="D162" s="35"/>
+      <c r="E162" s="35"/>
+      <c r="F162" s="35"/>
+      <c r="G162" s="35"/>
+      <c r="H162" s="35"/>
+      <c r="I162" s="35"/>
+      <c r="J162" s="35"/>
+      <c r="K162" s="35"/>
+      <c r="L162" s="36"/>
+      <c r="M162" s="57"/>
+    </row>
+    <row r="163" spans="1:13" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A163" s="34"/>
+      <c r="B163" s="35"/>
+      <c r="C163" s="35"/>
+      <c r="D163" s="35"/>
+      <c r="E163" s="35"/>
+      <c r="F163" s="35"/>
+      <c r="G163" s="35"/>
+      <c r="H163" s="35"/>
+      <c r="I163" s="35"/>
+      <c r="J163" s="35"/>
+      <c r="K163" s="35"/>
+      <c r="L163" s="36"/>
+      <c r="M163" s="57"/>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A164" s="52" t="s">
+        <v>240</v>
+      </c>
+      <c r="B164" s="1">
+        <v>7</v>
+      </c>
+      <c r="C164" s="35" t="s">
+        <v>253</v>
+      </c>
+      <c r="D164" s="35"/>
+      <c r="E164" s="35"/>
+      <c r="F164" s="35"/>
+      <c r="G164" s="35"/>
+      <c r="H164" s="35"/>
+      <c r="I164" s="35"/>
+      <c r="J164" s="35"/>
+      <c r="K164" s="35"/>
+      <c r="L164" s="36"/>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A165" s="52" t="s">
+        <v>245</v>
+      </c>
+      <c r="B165" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="C165" s="35"/>
+      <c r="D165" s="35"/>
+      <c r="E165" s="35" t="s">
+        <v>252</v>
+      </c>
+      <c r="F165" s="35"/>
+      <c r="G165" s="35"/>
+      <c r="H165" s="35"/>
+      <c r="I165" s="35"/>
+      <c r="J165" s="35"/>
+      <c r="K165" s="35"/>
+      <c r="L165" s="36"/>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A166" s="5" t="str">
+        <f>VLOOKUP($B$164,IF($B$164&gt;=11,BillNo3,IF($B$164&gt;=6,BillNo2,BillNo1)),COLUMN()+1,0)</f>
+        <v>Table</v>
+      </c>
+      <c r="B166" s="1">
+        <f>VLOOKUP($B$164,IF($B$164&gt;=11,BillNo3,IF($B$164&gt;=6,BillNo2,BillNo1)),COLUMN()+1,0)</f>
+        <v>70</v>
+      </c>
+      <c r="C166" s="35"/>
+      <c r="D166" s="35"/>
+      <c r="E166" s="35"/>
+      <c r="F166" s="35"/>
+      <c r="G166" s="35"/>
+      <c r="H166" s="35"/>
+      <c r="I166" s="35"/>
+      <c r="J166" s="35"/>
+      <c r="K166" s="35"/>
+      <c r="L166" s="36"/>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A167" s="34"/>
+      <c r="B167" s="35"/>
+      <c r="C167" s="35"/>
+      <c r="D167" s="35"/>
+      <c r="E167" s="35"/>
+      <c r="F167" s="35"/>
+      <c r="G167" s="35"/>
+      <c r="H167" s="35"/>
+      <c r="I167" s="35"/>
+      <c r="J167" s="35"/>
+      <c r="K167" s="35"/>
+      <c r="L167" s="36"/>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A168" s="34"/>
+      <c r="B168" s="35"/>
+      <c r="C168" s="35"/>
+      <c r="D168" s="35"/>
+      <c r="E168" s="35"/>
+      <c r="F168" s="35"/>
+      <c r="G168" s="35"/>
+      <c r="H168" s="35"/>
+      <c r="I168" s="35"/>
+      <c r="J168" s="35"/>
+      <c r="K168" s="35"/>
+      <c r="L168" s="36"/>
+    </row>
+    <row r="169" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A169" s="37"/>
+      <c r="B169" s="38"/>
+      <c r="C169" s="38"/>
+      <c r="D169" s="38"/>
+      <c r="E169" s="38"/>
+      <c r="F169" s="38"/>
+      <c r="G169" s="38"/>
+      <c r="H169" s="38"/>
+      <c r="I169" s="38"/>
+      <c r="J169" s="38"/>
+      <c r="K169" s="38"/>
+      <c r="L169" s="39"/>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B158">
+      <formula1>"1,2,3,4,5,6,7,8,9,10"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B164">
+      <formula1>"1,2,3,4,5,6,7,8,9,10,11,12,13,14,15"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="F1" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="G1" s="30"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="26">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="str">
+        <f>VLOOKUP($A2,Sheet4!$A$50:$B$55,2,0)</f>
+        <v>Jatin</v>
+      </c>
+      <c r="C2" s="1" t="e">
+        <f>VLOOKUP($A2,Sheet4!$A$50:$B$55,3,0)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D2" s="1" t="str">
+        <f>VLOOKUP($A2,Sheet4!$A$50:$B$55,2,0)</f>
+        <v>Jatin</v>
+      </c>
+      <c r="E2" s="1" t="str">
+        <f>VLOOKUP($A2,Sheet4!$A$50:$B$55,2,0)</f>
+        <v>Jatin</v>
+      </c>
+      <c r="F2" s="1" t="str">
+        <f>VLOOKUP($A2,Sheet4!$A$50:$B$55,2,0)</f>
+        <v>Jatin</v>
+      </c>
+      <c r="G2" s="26"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="26">
+        <v>3</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <f>VLOOKUP($A3,Sheet4!$A$50:$B$55,2,0)</f>
+        <v>Sam</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="26"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="26">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="str">
+        <f>VLOOKUP($A4,Sheet4!$A$50:$B$55,2,0)</f>
+        <v>Seema</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="26"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="26">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="str">
+        <f>VLOOKUP($A5,Sheet4!$A$50:$B$55,2,0)</f>
+        <v>Anu</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="26"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:N14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4733,72 +6746,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B1" s="73" t="s">
+      <c r="B1" s="94" t="s">
         <v>140</v>
       </c>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="73"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="94"/>
+      <c r="L1" s="94"/>
+      <c r="M1" s="94"/>
+      <c r="N1" s="94"/>
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73"/>
-      <c r="N2" s="73"/>
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="94"/>
+      <c r="K2" s="94"/>
+      <c r="L2" s="94"/>
+      <c r="M2" s="94"/>
+      <c r="N2" s="94"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B3" s="74" t="s">
+      <c r="B3" s="95" t="s">
         <v>141</v>
       </c>
-      <c r="C3" s="74"/>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="75" t="s">
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="96" t="s">
         <v>142</v>
       </c>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="76" t="s">
+      <c r="G3" s="96"/>
+      <c r="H3" s="96"/>
+      <c r="I3" s="96"/>
+      <c r="J3" s="97" t="s">
         <v>143</v>
       </c>
-      <c r="K3" s="76"/>
-      <c r="L3" s="76"/>
-      <c r="M3" s="76"/>
-      <c r="N3" s="76"/>
+      <c r="K3" s="97"/>
+      <c r="L3" s="97"/>
+      <c r="M3" s="97"/>
+      <c r="N3" s="97"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B4" s="74"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
-      <c r="I4" s="75"/>
-      <c r="J4" s="76"/>
-      <c r="K4" s="76"/>
-      <c r="L4" s="76"/>
-      <c r="M4" s="76"/>
-      <c r="N4" s="76"/>
+      <c r="B4" s="95"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="95"/>
+      <c r="E4" s="95"/>
+      <c r="F4" s="96"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="96"/>
+      <c r="J4" s="97"/>
+      <c r="K4" s="97"/>
+      <c r="L4" s="97"/>
+      <c r="M4" s="97"/>
+      <c r="N4" s="97"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B5" s="41" t="s">
@@ -5159,7 +7172,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5463,7 +7476,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:W57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5769,11 +7782,11 @@
       </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="E11" s="77" t="s">
+      <c r="E11" s="98" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="77"/>
-      <c r="G11" s="77"/>
+      <c r="F11" s="98"/>
+      <c r="G11" s="98"/>
       <c r="K11" t="s">
         <v>42</v>
       </c>
@@ -5908,10 +7921,10 @@
       <c r="G31" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="H31" s="77" t="s">
+      <c r="H31" s="98" t="s">
         <v>85</v>
       </c>
-      <c r="I31" s="77"/>
+      <c r="I31" s="98"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="26" t="s">
@@ -6114,18 +8127,18 @@
       <c r="N39" s="1"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="D40" s="78" t="s">
+      <c r="D40" s="99" t="s">
         <v>77</v>
       </c>
-      <c r="E40" s="78"/>
-      <c r="F40" s="78"/>
-      <c r="G40" s="78"/>
-      <c r="H40" s="78"/>
-      <c r="I40" s="78"/>
-      <c r="J40" s="53" t="s">
+      <c r="E40" s="99"/>
+      <c r="F40" s="99"/>
+      <c r="G40" s="99"/>
+      <c r="H40" s="99"/>
+      <c r="I40" s="99"/>
+      <c r="J40" s="74" t="s">
         <v>100</v>
       </c>
-      <c r="K40" s="53"/>
+      <c r="K40" s="74"/>
       <c r="L40" s="1">
         <f>SUMIF(A32:A39,"A?T",B32:B39)</f>
         <v>3</v>
@@ -6320,4 +8333,337 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:O18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="D1" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="F1" s="30" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="26">
+        <v>1</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2" s="26">
+        <v>12</v>
+      </c>
+      <c r="D2" s="26">
+        <v>14</v>
+      </c>
+      <c r="E2" s="26">
+        <v>32</v>
+      </c>
+      <c r="F2" s="26">
+        <f>SUM(C2,D2,E2)</f>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="26">
+        <v>2</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" s="26">
+        <v>62</v>
+      </c>
+      <c r="D3" s="26">
+        <v>76</v>
+      </c>
+      <c r="E3" s="26">
+        <v>20</v>
+      </c>
+      <c r="F3" s="26">
+        <f t="shared" ref="F3:F6" si="0">SUM(C3,D3,E3)</f>
+        <v>158</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="26">
+        <v>3</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="C4" s="26">
+        <v>33</v>
+      </c>
+      <c r="D4" s="26">
+        <v>27</v>
+      </c>
+      <c r="E4" s="26">
+        <v>94</v>
+      </c>
+      <c r="F4" s="26">
+        <f t="shared" si="0"/>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="26">
+        <v>4</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="C5" s="26">
+        <v>17</v>
+      </c>
+      <c r="D5" s="26">
+        <v>95</v>
+      </c>
+      <c r="E5" s="26">
+        <v>74</v>
+      </c>
+      <c r="F5" s="26">
+        <f t="shared" si="0"/>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="26">
+        <v>5</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="C6" s="26">
+        <v>10</v>
+      </c>
+      <c r="D6" s="26">
+        <v>97</v>
+      </c>
+      <c r="E6" s="26">
+        <v>78</v>
+      </c>
+      <c r="F6" s="26">
+        <f t="shared" si="0"/>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="B13" s="26">
+        <v>1</v>
+      </c>
+      <c r="C13" s="26">
+        <v>2</v>
+      </c>
+      <c r="D13" s="26">
+        <v>3</v>
+      </c>
+      <c r="E13" s="26">
+        <v>4</v>
+      </c>
+      <c r="F13" s="26">
+        <v>5</v>
+      </c>
+      <c r="J13" s="30" t="s">
+        <v>189</v>
+      </c>
+      <c r="K13" s="26">
+        <v>5</v>
+      </c>
+      <c r="L13" s="26">
+        <v>4</v>
+      </c>
+      <c r="M13" s="26">
+        <v>3</v>
+      </c>
+      <c r="N13" s="26">
+        <v>2</v>
+      </c>
+      <c r="O13" s="26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="F14" s="26" t="s">
+        <v>194</v>
+      </c>
+      <c r="J14" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="K14" s="29">
+        <f ca="1">HLOOKUP(K$14,resu,MATCH($J14,$A$13:$A$18,0),0)</f>
+        <v>0</v>
+      </c>
+      <c r="L14" s="29">
+        <f ca="1">HLOOKUP(L$14,res,ROW()-12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="29">
+        <f ca="1">HLOOKUP(M$14,res,ROW()-12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N14" s="29">
+        <f ca="1">HLOOKUP(N$14,res,ROW()-12,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O14" s="29">
+        <f ca="1">HLOOKUP(O$14,res,ROW()-12,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="B15" s="26">
+        <v>12</v>
+      </c>
+      <c r="C15" s="26">
+        <v>62</v>
+      </c>
+      <c r="D15" s="26">
+        <v>33</v>
+      </c>
+      <c r="E15" s="26">
+        <v>17</v>
+      </c>
+      <c r="F15" s="26">
+        <v>10</v>
+      </c>
+      <c r="J15" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="B16" s="26">
+        <v>14</v>
+      </c>
+      <c r="C16" s="26">
+        <v>76</v>
+      </c>
+      <c r="D16" s="26">
+        <v>27</v>
+      </c>
+      <c r="E16" s="26">
+        <v>95</v>
+      </c>
+      <c r="F16" s="26">
+        <v>97</v>
+      </c>
+      <c r="J16" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="29"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="B17" s="26">
+        <v>32</v>
+      </c>
+      <c r="C17" s="26">
+        <v>20</v>
+      </c>
+      <c r="D17" s="26">
+        <v>94</v>
+      </c>
+      <c r="E17" s="26">
+        <v>74</v>
+      </c>
+      <c r="F17" s="26">
+        <v>78</v>
+      </c>
+      <c r="J17" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="29"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="B18" s="26">
+        <f>SUM(B15,B16,B17)</f>
+        <v>58</v>
+      </c>
+      <c r="C18" s="26">
+        <f>SUM(C15,C16,C17)</f>
+        <v>158</v>
+      </c>
+      <c r="D18" s="26">
+        <f>SUM(D15,D16,D17)</f>
+        <v>154</v>
+      </c>
+      <c r="E18" s="26">
+        <f>SUM(E15,E16,E17)</f>
+        <v>186</v>
+      </c>
+      <c r="F18" s="26">
+        <f>SUM(F15,F16,F17)</f>
+        <v>185</v>
+      </c>
+      <c r="J18" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29"/>
+      <c r="N18" s="29"/>
+      <c r="O18" s="29"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>